--- a/resources/templates/system/deregistration_application.xlsx
+++ b/resources/templates/system/deregistration_application.xlsx
@@ -4959,322 +4959,7 @@
     <col width="11.125" customWidth="1" style="1" min="13" max="13"/>
     <col width="26" customWidth="1" style="1" min="14" max="14"/>
     <col width="1.375" customWidth="1" style="1" min="15" max="15"/>
-    <col width="9" customWidth="1" style="1" min="16" max="256"/>
-    <col width="10" customWidth="1" style="1" min="257" max="268"/>
-    <col width="9.875" customWidth="1" style="1" min="269" max="269"/>
-    <col width="26" customWidth="1" style="1" min="270" max="270"/>
-    <col width="1.375" customWidth="1" style="1" min="271" max="271"/>
-    <col width="9" customWidth="1" style="1" min="272" max="512"/>
-    <col width="10" customWidth="1" style="1" min="513" max="524"/>
-    <col width="9.875" customWidth="1" style="1" min="525" max="525"/>
-    <col width="26" customWidth="1" style="1" min="526" max="526"/>
-    <col width="1.375" customWidth="1" style="1" min="527" max="527"/>
-    <col width="9" customWidth="1" style="1" min="528" max="768"/>
-    <col width="10" customWidth="1" style="1" min="769" max="780"/>
-    <col width="9.875" customWidth="1" style="1" min="781" max="781"/>
-    <col width="26" customWidth="1" style="1" min="782" max="782"/>
-    <col width="1.375" customWidth="1" style="1" min="783" max="783"/>
-    <col width="9" customWidth="1" style="1" min="784" max="1024"/>
-    <col width="10" customWidth="1" style="1" min="1025" max="1036"/>
-    <col width="9.875" customWidth="1" style="1" min="1037" max="1037"/>
-    <col width="26" customWidth="1" style="1" min="1038" max="1038"/>
-    <col width="1.375" customWidth="1" style="1" min="1039" max="1039"/>
-    <col width="9" customWidth="1" style="1" min="1040" max="1280"/>
-    <col width="10" customWidth="1" style="1" min="1281" max="1292"/>
-    <col width="9.875" customWidth="1" style="1" min="1293" max="1293"/>
-    <col width="26" customWidth="1" style="1" min="1294" max="1294"/>
-    <col width="1.375" customWidth="1" style="1" min="1295" max="1295"/>
-    <col width="9" customWidth="1" style="1" min="1296" max="1536"/>
-    <col width="10" customWidth="1" style="1" min="1537" max="1548"/>
-    <col width="9.875" customWidth="1" style="1" min="1549" max="1549"/>
-    <col width="26" customWidth="1" style="1" min="1550" max="1550"/>
-    <col width="1.375" customWidth="1" style="1" min="1551" max="1551"/>
-    <col width="9" customWidth="1" style="1" min="1552" max="1792"/>
-    <col width="10" customWidth="1" style="1" min="1793" max="1804"/>
-    <col width="9.875" customWidth="1" style="1" min="1805" max="1805"/>
-    <col width="26" customWidth="1" style="1" min="1806" max="1806"/>
-    <col width="1.375" customWidth="1" style="1" min="1807" max="1807"/>
-    <col width="9" customWidth="1" style="1" min="1808" max="2048"/>
-    <col width="10" customWidth="1" style="1" min="2049" max="2060"/>
-    <col width="9.875" customWidth="1" style="1" min="2061" max="2061"/>
-    <col width="26" customWidth="1" style="1" min="2062" max="2062"/>
-    <col width="1.375" customWidth="1" style="1" min="2063" max="2063"/>
-    <col width="9" customWidth="1" style="1" min="2064" max="2304"/>
-    <col width="10" customWidth="1" style="1" min="2305" max="2316"/>
-    <col width="9.875" customWidth="1" style="1" min="2317" max="2317"/>
-    <col width="26" customWidth="1" style="1" min="2318" max="2318"/>
-    <col width="1.375" customWidth="1" style="1" min="2319" max="2319"/>
-    <col width="9" customWidth="1" style="1" min="2320" max="2560"/>
-    <col width="10" customWidth="1" style="1" min="2561" max="2572"/>
-    <col width="9.875" customWidth="1" style="1" min="2573" max="2573"/>
-    <col width="26" customWidth="1" style="1" min="2574" max="2574"/>
-    <col width="1.375" customWidth="1" style="1" min="2575" max="2575"/>
-    <col width="9" customWidth="1" style="1" min="2576" max="2816"/>
-    <col width="10" customWidth="1" style="1" min="2817" max="2828"/>
-    <col width="9.875" customWidth="1" style="1" min="2829" max="2829"/>
-    <col width="26" customWidth="1" style="1" min="2830" max="2830"/>
-    <col width="1.375" customWidth="1" style="1" min="2831" max="2831"/>
-    <col width="9" customWidth="1" style="1" min="2832" max="3072"/>
-    <col width="10" customWidth="1" style="1" min="3073" max="3084"/>
-    <col width="9.875" customWidth="1" style="1" min="3085" max="3085"/>
-    <col width="26" customWidth="1" style="1" min="3086" max="3086"/>
-    <col width="1.375" customWidth="1" style="1" min="3087" max="3087"/>
-    <col width="9" customWidth="1" style="1" min="3088" max="3328"/>
-    <col width="10" customWidth="1" style="1" min="3329" max="3340"/>
-    <col width="9.875" customWidth="1" style="1" min="3341" max="3341"/>
-    <col width="26" customWidth="1" style="1" min="3342" max="3342"/>
-    <col width="1.375" customWidth="1" style="1" min="3343" max="3343"/>
-    <col width="9" customWidth="1" style="1" min="3344" max="3584"/>
-    <col width="10" customWidth="1" style="1" min="3585" max="3596"/>
-    <col width="9.875" customWidth="1" style="1" min="3597" max="3597"/>
-    <col width="26" customWidth="1" style="1" min="3598" max="3598"/>
-    <col width="1.375" customWidth="1" style="1" min="3599" max="3599"/>
-    <col width="9" customWidth="1" style="1" min="3600" max="3840"/>
-    <col width="10" customWidth="1" style="1" min="3841" max="3852"/>
-    <col width="9.875" customWidth="1" style="1" min="3853" max="3853"/>
-    <col width="26" customWidth="1" style="1" min="3854" max="3854"/>
-    <col width="1.375" customWidth="1" style="1" min="3855" max="3855"/>
-    <col width="9" customWidth="1" style="1" min="3856" max="4096"/>
-    <col width="10" customWidth="1" style="1" min="4097" max="4108"/>
-    <col width="9.875" customWidth="1" style="1" min="4109" max="4109"/>
-    <col width="26" customWidth="1" style="1" min="4110" max="4110"/>
-    <col width="1.375" customWidth="1" style="1" min="4111" max="4111"/>
-    <col width="9" customWidth="1" style="1" min="4112" max="4352"/>
-    <col width="10" customWidth="1" style="1" min="4353" max="4364"/>
-    <col width="9.875" customWidth="1" style="1" min="4365" max="4365"/>
-    <col width="26" customWidth="1" style="1" min="4366" max="4366"/>
-    <col width="1.375" customWidth="1" style="1" min="4367" max="4367"/>
-    <col width="9" customWidth="1" style="1" min="4368" max="4608"/>
-    <col width="10" customWidth="1" style="1" min="4609" max="4620"/>
-    <col width="9.875" customWidth="1" style="1" min="4621" max="4621"/>
-    <col width="26" customWidth="1" style="1" min="4622" max="4622"/>
-    <col width="1.375" customWidth="1" style="1" min="4623" max="4623"/>
-    <col width="9" customWidth="1" style="1" min="4624" max="4864"/>
-    <col width="10" customWidth="1" style="1" min="4865" max="4876"/>
-    <col width="9.875" customWidth="1" style="1" min="4877" max="4877"/>
-    <col width="26" customWidth="1" style="1" min="4878" max="4878"/>
-    <col width="1.375" customWidth="1" style="1" min="4879" max="4879"/>
-    <col width="9" customWidth="1" style="1" min="4880" max="5120"/>
-    <col width="10" customWidth="1" style="1" min="5121" max="5132"/>
-    <col width="9.875" customWidth="1" style="1" min="5133" max="5133"/>
-    <col width="26" customWidth="1" style="1" min="5134" max="5134"/>
-    <col width="1.375" customWidth="1" style="1" min="5135" max="5135"/>
-    <col width="9" customWidth="1" style="1" min="5136" max="5376"/>
-    <col width="10" customWidth="1" style="1" min="5377" max="5388"/>
-    <col width="9.875" customWidth="1" style="1" min="5389" max="5389"/>
-    <col width="26" customWidth="1" style="1" min="5390" max="5390"/>
-    <col width="1.375" customWidth="1" style="1" min="5391" max="5391"/>
-    <col width="9" customWidth="1" style="1" min="5392" max="5632"/>
-    <col width="10" customWidth="1" style="1" min="5633" max="5644"/>
-    <col width="9.875" customWidth="1" style="1" min="5645" max="5645"/>
-    <col width="26" customWidth="1" style="1" min="5646" max="5646"/>
-    <col width="1.375" customWidth="1" style="1" min="5647" max="5647"/>
-    <col width="9" customWidth="1" style="1" min="5648" max="5888"/>
-    <col width="10" customWidth="1" style="1" min="5889" max="5900"/>
-    <col width="9.875" customWidth="1" style="1" min="5901" max="5901"/>
-    <col width="26" customWidth="1" style="1" min="5902" max="5902"/>
-    <col width="1.375" customWidth="1" style="1" min="5903" max="5903"/>
-    <col width="9" customWidth="1" style="1" min="5904" max="6144"/>
-    <col width="10" customWidth="1" style="1" min="6145" max="6156"/>
-    <col width="9.875" customWidth="1" style="1" min="6157" max="6157"/>
-    <col width="26" customWidth="1" style="1" min="6158" max="6158"/>
-    <col width="1.375" customWidth="1" style="1" min="6159" max="6159"/>
-    <col width="9" customWidth="1" style="1" min="6160" max="6400"/>
-    <col width="10" customWidth="1" style="1" min="6401" max="6412"/>
-    <col width="9.875" customWidth="1" style="1" min="6413" max="6413"/>
-    <col width="26" customWidth="1" style="1" min="6414" max="6414"/>
-    <col width="1.375" customWidth="1" style="1" min="6415" max="6415"/>
-    <col width="9" customWidth="1" style="1" min="6416" max="6656"/>
-    <col width="10" customWidth="1" style="1" min="6657" max="6668"/>
-    <col width="9.875" customWidth="1" style="1" min="6669" max="6669"/>
-    <col width="26" customWidth="1" style="1" min="6670" max="6670"/>
-    <col width="1.375" customWidth="1" style="1" min="6671" max="6671"/>
-    <col width="9" customWidth="1" style="1" min="6672" max="6912"/>
-    <col width="10" customWidth="1" style="1" min="6913" max="6924"/>
-    <col width="9.875" customWidth="1" style="1" min="6925" max="6925"/>
-    <col width="26" customWidth="1" style="1" min="6926" max="6926"/>
-    <col width="1.375" customWidth="1" style="1" min="6927" max="6927"/>
-    <col width="9" customWidth="1" style="1" min="6928" max="7168"/>
-    <col width="10" customWidth="1" style="1" min="7169" max="7180"/>
-    <col width="9.875" customWidth="1" style="1" min="7181" max="7181"/>
-    <col width="26" customWidth="1" style="1" min="7182" max="7182"/>
-    <col width="1.375" customWidth="1" style="1" min="7183" max="7183"/>
-    <col width="9" customWidth="1" style="1" min="7184" max="7424"/>
-    <col width="10" customWidth="1" style="1" min="7425" max="7436"/>
-    <col width="9.875" customWidth="1" style="1" min="7437" max="7437"/>
-    <col width="26" customWidth="1" style="1" min="7438" max="7438"/>
-    <col width="1.375" customWidth="1" style="1" min="7439" max="7439"/>
-    <col width="9" customWidth="1" style="1" min="7440" max="7680"/>
-    <col width="10" customWidth="1" style="1" min="7681" max="7692"/>
-    <col width="9.875" customWidth="1" style="1" min="7693" max="7693"/>
-    <col width="26" customWidth="1" style="1" min="7694" max="7694"/>
-    <col width="1.375" customWidth="1" style="1" min="7695" max="7695"/>
-    <col width="9" customWidth="1" style="1" min="7696" max="7936"/>
-    <col width="10" customWidth="1" style="1" min="7937" max="7948"/>
-    <col width="9.875" customWidth="1" style="1" min="7949" max="7949"/>
-    <col width="26" customWidth="1" style="1" min="7950" max="7950"/>
-    <col width="1.375" customWidth="1" style="1" min="7951" max="7951"/>
-    <col width="9" customWidth="1" style="1" min="7952" max="8192"/>
-    <col width="10" customWidth="1" style="1" min="8193" max="8204"/>
-    <col width="9.875" customWidth="1" style="1" min="8205" max="8205"/>
-    <col width="26" customWidth="1" style="1" min="8206" max="8206"/>
-    <col width="1.375" customWidth="1" style="1" min="8207" max="8207"/>
-    <col width="9" customWidth="1" style="1" min="8208" max="8448"/>
-    <col width="10" customWidth="1" style="1" min="8449" max="8460"/>
-    <col width="9.875" customWidth="1" style="1" min="8461" max="8461"/>
-    <col width="26" customWidth="1" style="1" min="8462" max="8462"/>
-    <col width="1.375" customWidth="1" style="1" min="8463" max="8463"/>
-    <col width="9" customWidth="1" style="1" min="8464" max="8704"/>
-    <col width="10" customWidth="1" style="1" min="8705" max="8716"/>
-    <col width="9.875" customWidth="1" style="1" min="8717" max="8717"/>
-    <col width="26" customWidth="1" style="1" min="8718" max="8718"/>
-    <col width="1.375" customWidth="1" style="1" min="8719" max="8719"/>
-    <col width="9" customWidth="1" style="1" min="8720" max="8960"/>
-    <col width="10" customWidth="1" style="1" min="8961" max="8972"/>
-    <col width="9.875" customWidth="1" style="1" min="8973" max="8973"/>
-    <col width="26" customWidth="1" style="1" min="8974" max="8974"/>
-    <col width="1.375" customWidth="1" style="1" min="8975" max="8975"/>
-    <col width="9" customWidth="1" style="1" min="8976" max="9216"/>
-    <col width="10" customWidth="1" style="1" min="9217" max="9228"/>
-    <col width="9.875" customWidth="1" style="1" min="9229" max="9229"/>
-    <col width="26" customWidth="1" style="1" min="9230" max="9230"/>
-    <col width="1.375" customWidth="1" style="1" min="9231" max="9231"/>
-    <col width="9" customWidth="1" style="1" min="9232" max="9472"/>
-    <col width="10" customWidth="1" style="1" min="9473" max="9484"/>
-    <col width="9.875" customWidth="1" style="1" min="9485" max="9485"/>
-    <col width="26" customWidth="1" style="1" min="9486" max="9486"/>
-    <col width="1.375" customWidth="1" style="1" min="9487" max="9487"/>
-    <col width="9" customWidth="1" style="1" min="9488" max="9728"/>
-    <col width="10" customWidth="1" style="1" min="9729" max="9740"/>
-    <col width="9.875" customWidth="1" style="1" min="9741" max="9741"/>
-    <col width="26" customWidth="1" style="1" min="9742" max="9742"/>
-    <col width="1.375" customWidth="1" style="1" min="9743" max="9743"/>
-    <col width="9" customWidth="1" style="1" min="9744" max="9984"/>
-    <col width="10" customWidth="1" style="1" min="9985" max="9996"/>
-    <col width="9.875" customWidth="1" style="1" min="9997" max="9997"/>
-    <col width="26" customWidth="1" style="1" min="9998" max="9998"/>
-    <col width="1.375" customWidth="1" style="1" min="9999" max="9999"/>
-    <col width="9" customWidth="1" style="1" min="10000" max="10240"/>
-    <col width="10" customWidth="1" style="1" min="10241" max="10252"/>
-    <col width="9.875" customWidth="1" style="1" min="10253" max="10253"/>
-    <col width="26" customWidth="1" style="1" min="10254" max="10254"/>
-    <col width="1.375" customWidth="1" style="1" min="10255" max="10255"/>
-    <col width="9" customWidth="1" style="1" min="10256" max="10496"/>
-    <col width="10" customWidth="1" style="1" min="10497" max="10508"/>
-    <col width="9.875" customWidth="1" style="1" min="10509" max="10509"/>
-    <col width="26" customWidth="1" style="1" min="10510" max="10510"/>
-    <col width="1.375" customWidth="1" style="1" min="10511" max="10511"/>
-    <col width="9" customWidth="1" style="1" min="10512" max="10752"/>
-    <col width="10" customWidth="1" style="1" min="10753" max="10764"/>
-    <col width="9.875" customWidth="1" style="1" min="10765" max="10765"/>
-    <col width="26" customWidth="1" style="1" min="10766" max="10766"/>
-    <col width="1.375" customWidth="1" style="1" min="10767" max="10767"/>
-    <col width="9" customWidth="1" style="1" min="10768" max="11008"/>
-    <col width="10" customWidth="1" style="1" min="11009" max="11020"/>
-    <col width="9.875" customWidth="1" style="1" min="11021" max="11021"/>
-    <col width="26" customWidth="1" style="1" min="11022" max="11022"/>
-    <col width="1.375" customWidth="1" style="1" min="11023" max="11023"/>
-    <col width="9" customWidth="1" style="1" min="11024" max="11264"/>
-    <col width="10" customWidth="1" style="1" min="11265" max="11276"/>
-    <col width="9.875" customWidth="1" style="1" min="11277" max="11277"/>
-    <col width="26" customWidth="1" style="1" min="11278" max="11278"/>
-    <col width="1.375" customWidth="1" style="1" min="11279" max="11279"/>
-    <col width="9" customWidth="1" style="1" min="11280" max="11520"/>
-    <col width="10" customWidth="1" style="1" min="11521" max="11532"/>
-    <col width="9.875" customWidth="1" style="1" min="11533" max="11533"/>
-    <col width="26" customWidth="1" style="1" min="11534" max="11534"/>
-    <col width="1.375" customWidth="1" style="1" min="11535" max="11535"/>
-    <col width="9" customWidth="1" style="1" min="11536" max="11776"/>
-    <col width="10" customWidth="1" style="1" min="11777" max="11788"/>
-    <col width="9.875" customWidth="1" style="1" min="11789" max="11789"/>
-    <col width="26" customWidth="1" style="1" min="11790" max="11790"/>
-    <col width="1.375" customWidth="1" style="1" min="11791" max="11791"/>
-    <col width="9" customWidth="1" style="1" min="11792" max="12032"/>
-    <col width="10" customWidth="1" style="1" min="12033" max="12044"/>
-    <col width="9.875" customWidth="1" style="1" min="12045" max="12045"/>
-    <col width="26" customWidth="1" style="1" min="12046" max="12046"/>
-    <col width="1.375" customWidth="1" style="1" min="12047" max="12047"/>
-    <col width="9" customWidth="1" style="1" min="12048" max="12288"/>
-    <col width="10" customWidth="1" style="1" min="12289" max="12300"/>
-    <col width="9.875" customWidth="1" style="1" min="12301" max="12301"/>
-    <col width="26" customWidth="1" style="1" min="12302" max="12302"/>
-    <col width="1.375" customWidth="1" style="1" min="12303" max="12303"/>
-    <col width="9" customWidth="1" style="1" min="12304" max="12544"/>
-    <col width="10" customWidth="1" style="1" min="12545" max="12556"/>
-    <col width="9.875" customWidth="1" style="1" min="12557" max="12557"/>
-    <col width="26" customWidth="1" style="1" min="12558" max="12558"/>
-    <col width="1.375" customWidth="1" style="1" min="12559" max="12559"/>
-    <col width="9" customWidth="1" style="1" min="12560" max="12800"/>
-    <col width="10" customWidth="1" style="1" min="12801" max="12812"/>
-    <col width="9.875" customWidth="1" style="1" min="12813" max="12813"/>
-    <col width="26" customWidth="1" style="1" min="12814" max="12814"/>
-    <col width="1.375" customWidth="1" style="1" min="12815" max="12815"/>
-    <col width="9" customWidth="1" style="1" min="12816" max="13056"/>
-    <col width="10" customWidth="1" style="1" min="13057" max="13068"/>
-    <col width="9.875" customWidth="1" style="1" min="13069" max="13069"/>
-    <col width="26" customWidth="1" style="1" min="13070" max="13070"/>
-    <col width="1.375" customWidth="1" style="1" min="13071" max="13071"/>
-    <col width="9" customWidth="1" style="1" min="13072" max="13312"/>
-    <col width="10" customWidth="1" style="1" min="13313" max="13324"/>
-    <col width="9.875" customWidth="1" style="1" min="13325" max="13325"/>
-    <col width="26" customWidth="1" style="1" min="13326" max="13326"/>
-    <col width="1.375" customWidth="1" style="1" min="13327" max="13327"/>
-    <col width="9" customWidth="1" style="1" min="13328" max="13568"/>
-    <col width="10" customWidth="1" style="1" min="13569" max="13580"/>
-    <col width="9.875" customWidth="1" style="1" min="13581" max="13581"/>
-    <col width="26" customWidth="1" style="1" min="13582" max="13582"/>
-    <col width="1.375" customWidth="1" style="1" min="13583" max="13583"/>
-    <col width="9" customWidth="1" style="1" min="13584" max="13824"/>
-    <col width="10" customWidth="1" style="1" min="13825" max="13836"/>
-    <col width="9.875" customWidth="1" style="1" min="13837" max="13837"/>
-    <col width="26" customWidth="1" style="1" min="13838" max="13838"/>
-    <col width="1.375" customWidth="1" style="1" min="13839" max="13839"/>
-    <col width="9" customWidth="1" style="1" min="13840" max="14080"/>
-    <col width="10" customWidth="1" style="1" min="14081" max="14092"/>
-    <col width="9.875" customWidth="1" style="1" min="14093" max="14093"/>
-    <col width="26" customWidth="1" style="1" min="14094" max="14094"/>
-    <col width="1.375" customWidth="1" style="1" min="14095" max="14095"/>
-    <col width="9" customWidth="1" style="1" min="14096" max="14336"/>
-    <col width="10" customWidth="1" style="1" min="14337" max="14348"/>
-    <col width="9.875" customWidth="1" style="1" min="14349" max="14349"/>
-    <col width="26" customWidth="1" style="1" min="14350" max="14350"/>
-    <col width="1.375" customWidth="1" style="1" min="14351" max="14351"/>
-    <col width="9" customWidth="1" style="1" min="14352" max="14592"/>
-    <col width="10" customWidth="1" style="1" min="14593" max="14604"/>
-    <col width="9.875" customWidth="1" style="1" min="14605" max="14605"/>
-    <col width="26" customWidth="1" style="1" min="14606" max="14606"/>
-    <col width="1.375" customWidth="1" style="1" min="14607" max="14607"/>
-    <col width="9" customWidth="1" style="1" min="14608" max="14848"/>
-    <col width="10" customWidth="1" style="1" min="14849" max="14860"/>
-    <col width="9.875" customWidth="1" style="1" min="14861" max="14861"/>
-    <col width="26" customWidth="1" style="1" min="14862" max="14862"/>
-    <col width="1.375" customWidth="1" style="1" min="14863" max="14863"/>
-    <col width="9" customWidth="1" style="1" min="14864" max="15104"/>
-    <col width="10" customWidth="1" style="1" min="15105" max="15116"/>
-    <col width="9.875" customWidth="1" style="1" min="15117" max="15117"/>
-    <col width="26" customWidth="1" style="1" min="15118" max="15118"/>
-    <col width="1.375" customWidth="1" style="1" min="15119" max="15119"/>
-    <col width="9" customWidth="1" style="1" min="15120" max="15360"/>
-    <col width="10" customWidth="1" style="1" min="15361" max="15372"/>
-    <col width="9.875" customWidth="1" style="1" min="15373" max="15373"/>
-    <col width="26" customWidth="1" style="1" min="15374" max="15374"/>
-    <col width="1.375" customWidth="1" style="1" min="15375" max="15375"/>
-    <col width="9" customWidth="1" style="1" min="15376" max="15616"/>
-    <col width="10" customWidth="1" style="1" min="15617" max="15628"/>
-    <col width="9.875" customWidth="1" style="1" min="15629" max="15629"/>
-    <col width="26" customWidth="1" style="1" min="15630" max="15630"/>
-    <col width="1.375" customWidth="1" style="1" min="15631" max="15631"/>
-    <col width="9" customWidth="1" style="1" min="15632" max="15872"/>
-    <col width="10" customWidth="1" style="1" min="15873" max="15884"/>
-    <col width="9.875" customWidth="1" style="1" min="15885" max="15885"/>
-    <col width="26" customWidth="1" style="1" min="15886" max="15886"/>
-    <col width="1.375" customWidth="1" style="1" min="15887" max="15887"/>
-    <col width="9" customWidth="1" style="1" min="15888" max="16128"/>
-    <col width="10" customWidth="1" style="1" min="16129" max="16140"/>
-    <col width="9.875" customWidth="1" style="1" min="16141" max="16141"/>
-    <col width="26" customWidth="1" style="1" min="16142" max="16142"/>
-    <col width="1.375" customWidth="1" style="1" min="16143" max="16143"/>
-    <col width="9" customWidth="1" style="1" min="16144" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="16" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" s="147">

--- a/resources/templates/system/deregistration_application.xlsx
+++ b/resources/templates/system/deregistration_application.xlsx
@@ -298,9 +298,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">경기도 시흥시 산기대학로 163, 328호(정왕동)</t>
-    </r>
+    <t>경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
   </si>
   <si>
     <r>
@@ -2797,12 +2795,8 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">경기도 시흥시 산기대학로 163, 328호(정왕동)</t>
-          </r>
-        </is>
+      <c r="C34" s="29" t="s">
+        <v>49</v>
       </c>
       <c r="D34" s="105"/>
       <c r="E34" s="105"/>
